--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q20_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0007175122759368553</v>
+        <v>0.0002699776656189117</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007175122759368553</v>
+        <v>0.0002699776656189117</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0007054420887510639</v>
+        <v>0.0002646305671867687</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007054420887510639</v>
+        <v>0.0002646305671867687</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0006941780164769226</v>
+        <v>0.0002599422808521607</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006941780164769226</v>
+        <v>0.0002599422808521607</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0006979415808150614</v>
+        <v>0.0002616766316286204</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0006979415808150614</v>
+        <v>0.0002616766316286204</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0007329790680320563</v>
+        <v>0.000276040335716004</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0007329790680320563</v>
+        <v>0.000276040335716004</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0008108375386422336</v>
+        <v>0.0003073320510131997</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008108375386422336</v>
+        <v>0.0003073320510131997</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0009437722568130141</v>
+        <v>0.0003600518465094426</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009437722568130141</v>
+        <v>0.0003600518465094426</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001133258992589172</v>
+        <v>0.0004344644623832708</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001133258992589172</v>
+        <v>0.0004344644623832708</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00136653477949101</v>
+        <v>0.0005252130294130056</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00136653477949101</v>
+        <v>0.0005252130294130056</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001626187874523213</v>
+        <v>0.0006250755325685277</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001626187874523213</v>
+        <v>0.0006250755325685277</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001891708019109061</v>
+        <v>0.000725958572022836</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001891708019109061</v>
+        <v>0.000725958572022836</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00215547649287565</v>
+        <v>0.0008253139014529917</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00215547649287565</v>
+        <v>0.0008253139014529917</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002446174122772873</v>
+        <v>0.0009350551137121953</v>
       </c>
       <c r="C14" t="n">
-        <v>0.002446174122772873</v>
+        <v>0.0009350551137121953</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.002773208388813673</v>
+        <v>0.001059437550471074</v>
       </c>
       <c r="C15" t="n">
-        <v>0.002773208388813673</v>
+        <v>0.001059437550471074</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00312309859676984</v>
+        <v>0.001193552087595202</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00312309859676984</v>
+        <v>0.001193552087595202</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003470222517878231</v>
+        <v>0.001327246425687975</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003470222517878231</v>
+        <v>0.001327246425687975</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.003779086137659759</v>
+        <v>0.001446588023069115</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003779086137659759</v>
+        <v>0.001446588023069115</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.004060785000478105</v>
+        <v>0.001555406332886368</v>
       </c>
       <c r="C19" t="n">
-        <v>0.004060785000478105</v>
+        <v>0.001555406332886368</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.004288963148215999</v>
+        <v>0.001643505748395514</v>
       </c>
       <c r="C20" t="n">
-        <v>0.004288963148215999</v>
+        <v>0.001643505748395514</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.004458813509706929</v>
+        <v>0.00170886957023003</v>
       </c>
       <c r="C21" t="n">
-        <v>0.004458813509706929</v>
+        <v>0.00170886957023003</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.004570832584096547</v>
+        <v>0.001751547320480745</v>
       </c>
       <c r="C22" t="n">
-        <v>0.004570832584096547</v>
+        <v>0.001751547320480745</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.004640749059036414</v>
+        <v>0.001778008981461623</v>
       </c>
       <c r="C23" t="n">
-        <v>0.004640749059036414</v>
+        <v>0.001778008981461623</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.004688185912419657</v>
+        <v>0.001795551048955098</v>
       </c>
       <c r="C24" t="n">
-        <v>0.004688185912419657</v>
+        <v>0.001795551048955098</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.004683395990775983</v>
+        <v>0.001793211806524594</v>
       </c>
       <c r="C25" t="n">
-        <v>0.004683395990775983</v>
+        <v>0.001793211806524594</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.00465026122740817</v>
+        <v>0.001780203077442463</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00465026122740817</v>
+        <v>0.001780203077442463</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.004597637367164082</v>
+        <v>0.001759741620610412</v>
       </c>
       <c r="C27" t="n">
-        <v>0.004597637367164082</v>
+        <v>0.001759741620610412</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.004517651261038653</v>
+        <v>0.001729926438133817</v>
       </c>
       <c r="C28" t="n">
-        <v>0.004517651261038653</v>
+        <v>0.001729926438133817</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.004456383006442847</v>
+        <v>0.00170717025086122</v>
       </c>
       <c r="C29" t="n">
-        <v>0.004456383006442847</v>
+        <v>0.00170717025086122</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.004329406494685257</v>
+        <v>0.001657196730893955</v>
       </c>
       <c r="C30" t="n">
-        <v>0.004329406494685257</v>
+        <v>0.001657196730893955</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.004236957228953546</v>
+        <v>0.001622602541795821</v>
       </c>
       <c r="C31" t="n">
-        <v>0.004236957228953546</v>
+        <v>0.001622602541795821</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
